--- a/load_and_merge_scripts/data/model.xlsx
+++ b/load_and_merge_scripts/data/model.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="R67ec631187e64436"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" r:id="R4cb03bb1a7984d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelScope" sheetId="3" r:id="R68677c4e1980449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="R998d46370e7f4b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" r:id="Ra26ce0f1d49e43ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelScope" sheetId="3" r:id="R5745c829ecc54c3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -665,13 +665,13 @@
         <x:v>model_description</x:v>
       </x:c>
       <x:c r="D1" s="47" t="str">
-        <x:v>silver_model_naming_template</x:v>
+        <x:v>silver_model_naming_instructions</x:v>
       </x:c>
       <x:c r="E1" s="47" t="str">
         <x:v>silver_model_audit_columns_template</x:v>
       </x:c>
       <x:c r="F1" s="47" t="str">
-        <x:v>gold_model_naming_template</x:v>
+        <x:v>gold_model_naming_instructions</x:v>
       </x:c>
       <x:c r="G1" s="47" t="str">
         <x:v>gold_model_technical_columns_template</x:v>

--- a/load_and_merge_scripts/data/model.xlsx
+++ b/load_and_merge_scripts/data/model.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="R998d46370e7f4b83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" r:id="Ra26ce0f1d49e43ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelScope" sheetId="3" r:id="R5745c829ecc54c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="R292607ad5dc646b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" r:id="R331d226fdfbf4801"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelInputScope" sheetId="3" r:id="R126f7b93d1054cb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -537,7 +537,7 @@
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>Model definitions and Model Scope. Load after operational.xlsx.</x:v>
+        <x:v>Model definitions and Model Input Scope. Load after operational.xlsx.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -619,10 +619,10 @@
         <x:v>410</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
-        <x:v>ModelScope</x:v>
+        <x:v>ModelInputScope</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
-        <x:v>model.model_scope</x:v>
+        <x:v>model.model_input_scope</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
         <x:v>model_tenant_code, model_name, object_tenant_code, object_system_code, object_connection_code, object_schema, object_name</x:v>
